--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R94e3ce5e1aec4795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R332ea9a181fe4178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R469c2d38998c4504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rd859bf829487400d"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R469c2d38998c4504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rd859bf829487400d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Rbdad62ce98ad48dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rc6efb73ec1584401"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Rbdad62ce98ad48dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rc6efb73ec1584401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R9f5131417dae472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R9880bd3bbd9d4e1c"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R9f5131417dae472f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R9880bd3bbd9d4e1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R9b059f899e1c4ca2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rd993825d4a7e428d"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R9b059f899e1c4ca2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rd993825d4a7e428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R4f2ff3aa07f6432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R3d84abf402ec46ef"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R4f2ff3aa07f6432d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R3d84abf402ec46ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R8c4de2554c6043b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rbab375ba3b544b89"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R8c4de2554c6043b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rbab375ba3b544b89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R272c284b7a6e4f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R999c9897ae564134"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R272c284b7a6e4f02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R999c9897ae564134"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R6ebf1f989e224dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Re2de390152d341f7"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R6ebf1f989e224dfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Re2de390152d341f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R338841717bba47f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Refb36576111e4e97"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R338841717bba47f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Refb36576111e4e97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R19c049400a4b4044"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R24e0c715cded470a"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R19c049400a4b4044"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R24e0c715cded470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Rda9b89a5497f464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rbefb789d46e3467c"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Rda9b89a5497f464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rbefb789d46e3467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R0909284adcb04bbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R8457c340b11f4dc2"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>
@@ -131,12 +131,12 @@
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Calibri"/>
+      <x:name val="Aptos"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:name val="Calibri"/>
+      <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">
@@ -193,6 +193,289 @@
 </x:table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="OfficeIMO Modern">
+  <a:themeElements>
+    <a:clrScheme name="Modern">
+      <a:dk1>
+        <a:srgbClr val="1B2433"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="5B6575"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="F6F8FB"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="3F64D7"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="DC7536"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="058E80"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="A52758"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="3F2F6B"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="255319"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="3F64D7"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="A52758"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Modern">
+      <a:majorFont>
+        <a:latin typeface="Aptos"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R0909284adcb04bbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R8457c340b11f4dc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R7d354a2abb994629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R9ae5efcf551d43b9"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R7d354a2abb994629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R9ae5efcf551d43b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R6b512fab774c46f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R65f17a3291464f0a"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R6b512fab774c46f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R65f17a3291464f0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R8f5d83474d604efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R25aa08cc020d4cb5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R8f5d83474d604efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R25aa08cc020d4cb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Rb087f1a0670a4ef4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R38530710620d4f2d"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Rb087f1a0670a4ef4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R38530710620d4f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R38e226814f3f4301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R6e70400e8b03499c"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R38e226814f3f4301"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R6e70400e8b03499c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Reaf658a1009d4559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Re34f92396d664b9c"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Reaf658a1009d4559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Re34f92396d664b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R166c1301dd4e4fb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R3f03dd8a171b40a8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="Rda9b89a5497f464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rbefb789d46e3467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R714e40f2fa4f4bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R462c3d77187c4d06"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>

--- a/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
+++ b/Website/static/downloads/showcase/pswriteoffice/project-delivery-pack.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R166c1301dd4e4fb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="R3f03dd8a171b40a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="1" r:id="R00bd0ccede3a4af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="2" r:id="Rc4489b2445154a87"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'Review'!$A$1:$B$7</x:definedName>
